--- a/ig/nr-add-alimentation-bundle/StructureDefinition-mesures-observation-head-circumference.xlsx
+++ b/ig/nr-add-alimentation-bundle/StructureDefinition-mesures-observation-head-circumference.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-06-13T09:15:07+00:00</t>
+    <t>2023-06-13T09:23:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-add-alimentation-bundle/StructureDefinition-mesures-observation-head-circumference.xlsx
+++ b/ig/nr-add-alimentation-bundle/StructureDefinition-mesures-observation-head-circumference.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-06-13T09:23:37+00:00</t>
+    <t>2023-06-13T09:35:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-add-alimentation-bundle/StructureDefinition-mesures-observation-head-circumference.xlsx
+++ b/ig/nr-add-alimentation-bundle/StructureDefinition-mesures-observation-head-circumference.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-06-13T09:35:33+00:00</t>
+    <t>2023-06-13T09:42:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-add-alimentation-bundle/StructureDefinition-mesures-observation-head-circumference.xlsx
+++ b/ig/nr-add-alimentation-bundle/StructureDefinition-mesures-observation-head-circumference.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-06-13T09:42:48+00:00</t>
+    <t>2023-07-03T07:58:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-add-alimentation-bundle/StructureDefinition-mesures-observation-head-circumference.xlsx
+++ b/ig/nr-add-alimentation-bundle/StructureDefinition-mesures-observation-head-circumference.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3527" uniqueCount="614">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3528" uniqueCount="613">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-07-03T07:58:25+00:00</t>
+    <t>2023-07-18T09:37:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1243,10 +1243,6 @@
   </si>
   <si>
     <t>9. SHALL contain exactly one [1..1] value with @xsi:type="PQ" (CONF:7305).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">type:$this}
-</t>
   </si>
   <si>
     <t>ele-1
@@ -9003,14 +8999,16 @@
         <v>36</v>
       </c>
       <c r="AB56" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="AC56" s="2"/>
+        <v>36</v>
+      </c>
+      <c r="AC56" t="s" s="2">
+        <v>36</v>
+      </c>
       <c r="AD56" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AE56" t="s" s="2">
-        <v>75</v>
+        <v>36</v>
       </c>
       <c r="AF56" t="s" s="2">
         <v>387</v>
@@ -9022,7 +9020,7 @@
         <v>46</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="AJ56" t="s" s="2">
         <v>59</v>
@@ -9031,27 +9029,27 @@
         <v>36</v>
       </c>
       <c r="AL56" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="AM56" t="s" s="2">
         <v>394</v>
       </c>
-      <c r="AM56" t="s" s="2">
+      <c r="AN56" t="s" s="2">
         <v>395</v>
       </c>
-      <c r="AN56" t="s" s="2">
+      <c r="AO56" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AP56" t="s" s="2">
         <v>396</v>
-      </c>
-      <c r="AO56" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AP56" t="s" s="2">
-        <v>397</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9166,10 +9164,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9286,10 +9284,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9312,19 +9310,19 @@
         <v>47</v>
       </c>
       <c r="K59" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="L59" t="s" s="2">
         <v>401</v>
       </c>
-      <c r="L59" t="s" s="2">
+      <c r="M59" t="s" s="2">
         <v>402</v>
       </c>
-      <c r="M59" t="s" s="2">
+      <c r="N59" t="s" s="2">
         <v>403</v>
       </c>
-      <c r="N59" t="s" s="2">
+      <c r="O59" t="s" s="2">
         <v>404</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>405</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>36</v>
@@ -9373,7 +9371,7 @@
         <v>36</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>34</v>
@@ -9394,10 +9392,10 @@
         <v>36</v>
       </c>
       <c r="AM59" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="AN59" t="s" s="2">
         <v>407</v>
-      </c>
-      <c r="AN59" t="s" s="2">
-        <v>408</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>36</v>
@@ -9408,10 +9406,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9437,22 +9435,22 @@
         <v>126</v>
       </c>
       <c r="L60" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="M60" t="s" s="2">
         <v>410</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>411</v>
       </c>
       <c r="N60" t="s" s="2">
         <v>261</v>
       </c>
       <c r="O60" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="P60" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="Q60" t="s" s="2">
         <v>412</v>
-      </c>
-      <c r="P60" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="Q60" t="s" s="2">
-        <v>413</v>
       </c>
       <c r="R60" t="s" s="2">
         <v>36</v>
@@ -9476,28 +9474,28 @@
         <v>200</v>
       </c>
       <c r="Y60" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="Z60" t="s" s="2">
         <v>414</v>
       </c>
-      <c r="Z60" t="s" s="2">
+      <c r="AA60" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AB60" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AC60" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AD60" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AE60" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AF60" t="s" s="2">
         <v>415</v>
-      </c>
-      <c r="AA60" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AB60" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AC60" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AD60" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AE60" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AF60" t="s" s="2">
-        <v>416</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>34</v>
@@ -9518,10 +9516,10 @@
         <v>36</v>
       </c>
       <c r="AM60" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="AN60" t="s" s="2">
         <v>417</v>
-      </c>
-      <c r="AN60" t="s" s="2">
-        <v>418</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>36</v>
@@ -9532,10 +9530,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9561,16 +9559,16 @@
         <v>62</v>
       </c>
       <c r="L61" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="M61" t="s" s="2">
         <v>420</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>421</v>
       </c>
       <c r="N61" t="s" s="2">
         <v>261</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>36</v>
@@ -9580,46 +9578,46 @@
         <v>36</v>
       </c>
       <c r="S61" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="T61" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="U61" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="V61" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="W61" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="X61" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="Y61" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="Z61" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AA61" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AB61" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AC61" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AD61" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AE61" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AF61" t="s" s="2">
         <v>423</v>
-      </c>
-      <c r="T61" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="U61" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="V61" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="W61" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="X61" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="Y61" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="Z61" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AA61" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AB61" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AC61" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AD61" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AE61" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AF61" t="s" s="2">
-        <v>424</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>34</v>
@@ -9640,10 +9638,10 @@
         <v>36</v>
       </c>
       <c r="AM61" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="AN61" t="s" s="2">
         <v>425</v>
-      </c>
-      <c r="AN61" t="s" s="2">
-        <v>426</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>36</v>
@@ -9654,10 +9652,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9683,16 +9681,16 @@
         <v>90</v>
       </c>
       <c r="L62" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="M62" t="s" s="2">
         <v>428</v>
       </c>
-      <c r="M62" t="s" s="2">
+      <c r="N62" t="s" s="2">
         <v>429</v>
       </c>
-      <c r="N62" t="s" s="2">
+      <c r="O62" t="s" s="2">
         <v>430</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>431</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>36</v>
@@ -9702,46 +9700,46 @@
         <v>36</v>
       </c>
       <c r="S62" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="T62" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="U62" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="V62" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="W62" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="X62" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="Y62" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="Z62" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AA62" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AB62" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AC62" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AD62" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AE62" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AF62" t="s" s="2">
         <v>432</v>
-      </c>
-      <c r="T62" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="U62" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="V62" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="W62" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="X62" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="Y62" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="Z62" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AA62" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AB62" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AC62" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AD62" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AE62" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AF62" t="s" s="2">
-        <v>433</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>34</v>
@@ -9750,7 +9748,7 @@
         <v>46</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>59</v>
@@ -9762,10 +9760,10 @@
         <v>36</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>36</v>
@@ -9776,10 +9774,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9805,16 +9803,16 @@
         <v>126</v>
       </c>
       <c r="L63" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="M63" t="s" s="2">
         <v>437</v>
       </c>
-      <c r="M63" t="s" s="2">
+      <c r="N63" t="s" s="2">
         <v>438</v>
       </c>
-      <c r="N63" t="s" s="2">
+      <c r="O63" t="s" s="2">
         <v>439</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>440</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>36</v>
@@ -9863,7 +9861,7 @@
         <v>36</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>34</v>
@@ -9884,10 +9882,10 @@
         <v>36</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>36</v>
@@ -9898,10 +9896,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9927,16 +9925,16 @@
         <v>209</v>
       </c>
       <c r="L64" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="M64" t="s" s="2">
         <v>444</v>
       </c>
-      <c r="M64" t="s" s="2">
+      <c r="N64" t="s" s="2">
         <v>445</v>
       </c>
-      <c r="N64" t="s" s="2">
+      <c r="O64" t="s" s="2">
         <v>446</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>447</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>36</v>
@@ -9964,11 +9962,11 @@
         <v>106</v>
       </c>
       <c r="Y64" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="Z64" t="s" s="2">
         <v>448</v>
       </c>
-      <c r="Z64" t="s" s="2">
-        <v>449</v>
-      </c>
       <c r="AA64" t="s" s="2">
         <v>36</v>
       </c>
@@ -9985,7 +9983,7 @@
         <v>36</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>34</v>
@@ -9994,7 +9992,7 @@
         <v>46</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="AJ64" t="s" s="2">
         <v>59</v>
@@ -10009,7 +10007,7 @@
         <v>60</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>36</v>
@@ -10020,14 +10018,14 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
@@ -10049,16 +10047,16 @@
         <v>209</v>
       </c>
       <c r="L65" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="M65" t="s" s="2">
         <v>454</v>
       </c>
-      <c r="M65" t="s" s="2">
+      <c r="N65" t="s" s="2">
         <v>455</v>
       </c>
-      <c r="N65" t="s" s="2">
+      <c r="O65" t="s" s="2">
         <v>456</v>
-      </c>
-      <c r="O65" t="s" s="2">
-        <v>457</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>36</v>
@@ -10086,11 +10084,11 @@
         <v>106</v>
       </c>
       <c r="Y65" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="Z65" t="s" s="2">
         <v>458</v>
       </c>
-      <c r="Z65" t="s" s="2">
-        <v>459</v>
-      </c>
       <c r="AA65" t="s" s="2">
         <v>36</v>
       </c>
@@ -10107,7 +10105,7 @@
         <v>36</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>34</v>
@@ -10125,27 +10123,27 @@
         <v>36</v>
       </c>
       <c r="AL65" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="AM65" t="s" s="2">
         <v>460</v>
       </c>
-      <c r="AM65" t="s" s="2">
+      <c r="AN65" t="s" s="2">
         <v>461</v>
       </c>
-      <c r="AN65" t="s" s="2">
+      <c r="AO65" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AP65" t="s" s="2">
         <v>462</v>
-      </c>
-      <c r="AO65" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AP65" t="s" s="2">
-        <v>463</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10168,19 +10166,19 @@
         <v>36</v>
       </c>
       <c r="K66" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="L66" t="s" s="2">
         <v>465</v>
       </c>
-      <c r="L66" t="s" s="2">
+      <c r="M66" t="s" s="2">
         <v>466</v>
       </c>
-      <c r="M66" t="s" s="2">
+      <c r="N66" t="s" s="2">
         <v>467</v>
       </c>
-      <c r="N66" t="s" s="2">
+      <c r="O66" t="s" s="2">
         <v>468</v>
-      </c>
-      <c r="O66" t="s" s="2">
-        <v>469</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>36</v>
@@ -10229,7 +10227,7 @@
         <v>36</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>34</v>
@@ -10250,10 +10248,10 @@
         <v>36</v>
       </c>
       <c r="AM66" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="AN66" t="s" s="2">
         <v>470</v>
-      </c>
-      <c r="AN66" t="s" s="2">
-        <v>471</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>36</v>
@@ -10264,10 +10262,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10293,13 +10291,13 @@
         <v>209</v>
       </c>
       <c r="L67" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="M67" t="s" s="2">
         <v>473</v>
       </c>
-      <c r="M67" t="s" s="2">
+      <c r="N67" t="s" s="2">
         <v>474</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>475</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -10328,11 +10326,11 @@
         <v>116</v>
       </c>
       <c r="Y67" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="Z67" t="s" s="2">
         <v>476</v>
       </c>
-      <c r="Z67" t="s" s="2">
-        <v>477</v>
-      </c>
       <c r="AA67" t="s" s="2">
         <v>36</v>
       </c>
@@ -10349,7 +10347,7 @@
         <v>36</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>34</v>
@@ -10367,27 +10365,27 @@
         <v>36</v>
       </c>
       <c r="AL67" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="AM67" t="s" s="2">
         <v>478</v>
       </c>
-      <c r="AM67" t="s" s="2">
+      <c r="AN67" t="s" s="2">
         <v>479</v>
       </c>
-      <c r="AN67" t="s" s="2">
+      <c r="AO67" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AP67" t="s" s="2">
         <v>480</v>
-      </c>
-      <c r="AO67" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AP67" t="s" s="2">
-        <v>481</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10413,16 +10411,16 @@
         <v>209</v>
       </c>
       <c r="L68" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="M68" t="s" s="2">
         <v>483</v>
       </c>
-      <c r="M68" t="s" s="2">
+      <c r="N68" t="s" s="2">
         <v>484</v>
       </c>
-      <c r="N68" t="s" s="2">
+      <c r="O68" t="s" s="2">
         <v>485</v>
-      </c>
-      <c r="O68" t="s" s="2">
-        <v>486</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>36</v>
@@ -10450,11 +10448,11 @@
         <v>116</v>
       </c>
       <c r="Y68" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="Z68" t="s" s="2">
         <v>487</v>
       </c>
-      <c r="Z68" t="s" s="2">
-        <v>488</v>
-      </c>
       <c r="AA68" t="s" s="2">
         <v>36</v>
       </c>
@@ -10471,7 +10469,7 @@
         <v>36</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>34</v>
@@ -10492,10 +10490,10 @@
         <v>36</v>
       </c>
       <c r="AM68" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="AN68" t="s" s="2">
         <v>489</v>
-      </c>
-      <c r="AN68" t="s" s="2">
-        <v>490</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>36</v>
@@ -10506,10 +10504,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10532,16 +10530,16 @@
         <v>36</v>
       </c>
       <c r="K69" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="L69" t="s" s="2">
         <v>492</v>
       </c>
-      <c r="L69" t="s" s="2">
+      <c r="M69" t="s" s="2">
         <v>493</v>
       </c>
-      <c r="M69" t="s" s="2">
+      <c r="N69" t="s" s="2">
         <v>494</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>495</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -10591,7 +10589,7 @@
         <v>36</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>34</v>
@@ -10609,27 +10607,27 @@
         <v>36</v>
       </c>
       <c r="AL69" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="AM69" t="s" s="2">
         <v>496</v>
       </c>
-      <c r="AM69" t="s" s="2">
+      <c r="AN69" t="s" s="2">
         <v>497</v>
       </c>
-      <c r="AN69" t="s" s="2">
+      <c r="AO69" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AP69" t="s" s="2">
         <v>498</v>
-      </c>
-      <c r="AO69" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AP69" t="s" s="2">
-        <v>499</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10652,16 +10650,16 @@
         <v>36</v>
       </c>
       <c r="K70" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="L70" t="s" s="2">
         <v>501</v>
       </c>
-      <c r="L70" t="s" s="2">
+      <c r="M70" t="s" s="2">
         <v>502</v>
       </c>
-      <c r="M70" t="s" s="2">
+      <c r="N70" t="s" s="2">
         <v>503</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>504</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -10711,7 +10709,7 @@
         <v>36</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>34</v>
@@ -10729,27 +10727,27 @@
         <v>36</v>
       </c>
       <c r="AL70" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="AM70" t="s" s="2">
         <v>505</v>
       </c>
-      <c r="AM70" t="s" s="2">
+      <c r="AN70" t="s" s="2">
         <v>506</v>
       </c>
-      <c r="AN70" t="s" s="2">
+      <c r="AO70" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AP70" t="s" s="2">
         <v>507</v>
-      </c>
-      <c r="AO70" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AP70" t="s" s="2">
-        <v>508</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10772,19 +10770,19 @@
         <v>36</v>
       </c>
       <c r="K71" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="L71" t="s" s="2">
         <v>510</v>
       </c>
-      <c r="L71" t="s" s="2">
+      <c r="M71" t="s" s="2">
         <v>511</v>
       </c>
-      <c r="M71" t="s" s="2">
+      <c r="N71" t="s" s="2">
         <v>512</v>
       </c>
-      <c r="N71" t="s" s="2">
+      <c r="O71" t="s" s="2">
         <v>513</v>
-      </c>
-      <c r="O71" t="s" s="2">
-        <v>514</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>36</v>
@@ -10833,7 +10831,7 @@
         <v>36</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>34</v>
@@ -10845,19 +10843,19 @@
         <v>58</v>
       </c>
       <c r="AJ71" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="AK71" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AL71" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AM71" t="s" s="2">
         <v>515</v>
       </c>
-      <c r="AK71" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AL71" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AM71" t="s" s="2">
+      <c r="AN71" t="s" s="2">
         <v>516</v>
-      </c>
-      <c r="AN71" t="s" s="2">
-        <v>517</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>36</v>
@@ -10868,10 +10866,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10986,10 +10984,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11106,14 +11104,14 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -11135,10 +11133,10 @@
         <v>69</v>
       </c>
       <c r="L74" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="M74" t="s" s="2">
         <v>522</v>
-      </c>
-      <c r="M74" t="s" s="2">
-        <v>523</v>
       </c>
       <c r="N74" t="s" s="2">
         <v>72</v>
@@ -11193,7 +11191,7 @@
         <v>36</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>34</v>
@@ -11228,10 +11226,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11254,16 +11252,16 @@
         <v>36</v>
       </c>
       <c r="K75" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="L75" t="s" s="2">
         <v>526</v>
       </c>
-      <c r="L75" t="s" s="2">
+      <c r="M75" t="s" s="2">
         <v>527</v>
       </c>
-      <c r="M75" t="s" s="2">
+      <c r="N75" t="s" s="2">
         <v>528</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>529</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -11313,7 +11311,7 @@
         <v>36</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>34</v>
@@ -11322,22 +11320,22 @@
         <v>46</v>
       </c>
       <c r="AI75" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="AJ75" t="s" s="2">
         <v>530</v>
       </c>
-      <c r="AJ75" t="s" s="2">
+      <c r="AK75" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AL75" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AM75" t="s" s="2">
         <v>531</v>
       </c>
-      <c r="AK75" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AL75" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AM75" t="s" s="2">
+      <c r="AN75" t="s" s="2">
         <v>532</v>
-      </c>
-      <c r="AN75" t="s" s="2">
-        <v>533</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>36</v>
@@ -11348,10 +11346,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11374,16 +11372,16 @@
         <v>36</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="L76" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="M76" t="s" s="2">
         <v>535</v>
       </c>
-      <c r="M76" t="s" s="2">
-        <v>536</v>
-      </c>
       <c r="N76" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -11433,7 +11431,7 @@
         <v>36</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>34</v>
@@ -11442,22 +11440,22 @@
         <v>46</v>
       </c>
       <c r="AI76" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="AJ76" t="s" s="2">
         <v>530</v>
       </c>
-      <c r="AJ76" t="s" s="2">
+      <c r="AK76" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AL76" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AM76" t="s" s="2">
         <v>531</v>
       </c>
-      <c r="AK76" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AL76" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AM76" t="s" s="2">
-        <v>532</v>
-      </c>
       <c r="AN76" t="s" s="2">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>36</v>
@@ -11468,10 +11466,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11497,16 +11495,16 @@
         <v>209</v>
       </c>
       <c r="L77" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="M77" t="s" s="2">
         <v>539</v>
       </c>
-      <c r="M77" t="s" s="2">
+      <c r="N77" t="s" s="2">
         <v>540</v>
       </c>
-      <c r="N77" t="s" s="2">
+      <c r="O77" t="s" s="2">
         <v>541</v>
-      </c>
-      <c r="O77" t="s" s="2">
-        <v>542</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>36</v>
@@ -11534,11 +11532,11 @@
         <v>130</v>
       </c>
       <c r="Y77" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="Z77" t="s" s="2">
         <v>543</v>
       </c>
-      <c r="Z77" t="s" s="2">
-        <v>544</v>
-      </c>
       <c r="AA77" t="s" s="2">
         <v>36</v>
       </c>
@@ -11555,7 +11553,7 @@
         <v>36</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>34</v>
@@ -11573,13 +11571,13 @@
         <v>36</v>
       </c>
       <c r="AL77" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="AM77" t="s" s="2">
         <v>545</v>
       </c>
-      <c r="AM77" t="s" s="2">
-        <v>546</v>
-      </c>
       <c r="AN77" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>36</v>
@@ -11590,10 +11588,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11619,16 +11617,16 @@
         <v>209</v>
       </c>
       <c r="L78" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="M78" t="s" s="2">
         <v>548</v>
       </c>
-      <c r="M78" t="s" s="2">
+      <c r="N78" t="s" s="2">
         <v>549</v>
       </c>
-      <c r="N78" t="s" s="2">
+      <c r="O78" t="s" s="2">
         <v>550</v>
-      </c>
-      <c r="O78" t="s" s="2">
-        <v>551</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>36</v>
@@ -11656,11 +11654,11 @@
         <v>116</v>
       </c>
       <c r="Y78" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="Z78" t="s" s="2">
         <v>552</v>
       </c>
-      <c r="Z78" t="s" s="2">
-        <v>553</v>
-      </c>
       <c r="AA78" t="s" s="2">
         <v>36</v>
       </c>
@@ -11677,7 +11675,7 @@
         <v>36</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>34</v>
@@ -11695,13 +11693,13 @@
         <v>36</v>
       </c>
       <c r="AL78" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="AM78" t="s" s="2">
         <v>545</v>
       </c>
-      <c r="AM78" t="s" s="2">
-        <v>546</v>
-      </c>
       <c r="AN78" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>36</v>
@@ -11712,10 +11710,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11738,19 +11736,19 @@
         <v>36</v>
       </c>
       <c r="K79" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="L79" t="s" s="2">
         <v>555</v>
       </c>
-      <c r="L79" t="s" s="2">
+      <c r="M79" t="s" s="2">
         <v>556</v>
       </c>
-      <c r="M79" t="s" s="2">
+      <c r="N79" t="s" s="2">
         <v>557</v>
       </c>
-      <c r="N79" t="s" s="2">
+      <c r="O79" t="s" s="2">
         <v>558</v>
-      </c>
-      <c r="O79" t="s" s="2">
-        <v>559</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>36</v>
@@ -11799,7 +11797,7 @@
         <v>36</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>34</v>
@@ -11811,19 +11809,19 @@
         <v>58</v>
       </c>
       <c r="AJ79" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="AK79" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AL79" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AM79" t="s" s="2">
         <v>560</v>
       </c>
-      <c r="AK79" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AL79" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AM79" t="s" s="2">
+      <c r="AN79" t="s" s="2">
         <v>561</v>
-      </c>
-      <c r="AN79" t="s" s="2">
-        <v>562</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>36</v>
@@ -11834,10 +11832,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11863,10 +11861,10 @@
         <v>62</v>
       </c>
       <c r="L80" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="M80" t="s" s="2">
         <v>564</v>
-      </c>
-      <c r="M80" t="s" s="2">
-        <v>565</v>
       </c>
       <c r="N80" t="s" s="2">
         <v>261</v>
@@ -11919,7 +11917,7 @@
         <v>36</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>34</v>
@@ -11940,10 +11938,10 @@
         <v>36</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>36</v>
@@ -11954,10 +11952,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11980,16 +11978,16 @@
         <v>47</v>
       </c>
       <c r="K81" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="L81" t="s" s="2">
         <v>568</v>
       </c>
-      <c r="L81" t="s" s="2">
+      <c r="M81" t="s" s="2">
         <v>569</v>
       </c>
-      <c r="M81" t="s" s="2">
+      <c r="N81" t="s" s="2">
         <v>570</v>
-      </c>
-      <c r="N81" t="s" s="2">
-        <v>571</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -12039,7 +12037,7 @@
         <v>36</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>34</v>
@@ -12060,10 +12058,10 @@
         <v>36</v>
       </c>
       <c r="AM81" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="AN81" t="s" s="2">
         <v>572</v>
-      </c>
-      <c r="AN81" t="s" s="2">
-        <v>573</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>36</v>
@@ -12074,10 +12072,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12100,16 +12098,16 @@
         <v>47</v>
       </c>
       <c r="K82" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="L82" t="s" s="2">
         <v>575</v>
       </c>
-      <c r="L82" t="s" s="2">
+      <c r="M82" t="s" s="2">
         <v>576</v>
       </c>
-      <c r="M82" t="s" s="2">
+      <c r="N82" t="s" s="2">
         <v>577</v>
-      </c>
-      <c r="N82" t="s" s="2">
-        <v>578</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -12159,7 +12157,7 @@
         <v>36</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>34</v>
@@ -12180,10 +12178,10 @@
         <v>36</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>36</v>
@@ -12194,10 +12192,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12220,19 +12218,19 @@
         <v>47</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="L83" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="M83" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="N83" t="s" s="2">
         <v>581</v>
       </c>
-      <c r="M83" t="s" s="2">
-        <v>581</v>
-      </c>
-      <c r="N83" t="s" s="2">
+      <c r="O83" t="s" s="2">
         <v>582</v>
-      </c>
-      <c r="O83" t="s" s="2">
-        <v>583</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>36</v>
@@ -12281,7 +12279,7 @@
         <v>36</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>34</v>
@@ -12293,19 +12291,19 @@
         <v>58</v>
       </c>
       <c r="AJ83" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="AK83" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AL83" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AM83" t="s" s="2">
         <v>584</v>
       </c>
-      <c r="AK83" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AL83" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AM83" t="s" s="2">
+      <c r="AN83" t="s" s="2">
         <v>585</v>
-      </c>
-      <c r="AN83" t="s" s="2">
-        <v>586</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>36</v>
@@ -12316,10 +12314,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12434,10 +12432,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12554,14 +12552,14 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
@@ -12583,10 +12581,10 @@
         <v>69</v>
       </c>
       <c r="L86" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="M86" t="s" s="2">
         <v>522</v>
-      </c>
-      <c r="M86" t="s" s="2">
-        <v>523</v>
       </c>
       <c r="N86" t="s" s="2">
         <v>72</v>
@@ -12641,7 +12639,7 @@
         <v>36</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>34</v>
@@ -12676,10 +12674,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12705,16 +12703,16 @@
         <v>209</v>
       </c>
       <c r="L87" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="M87" t="s" s="2">
         <v>591</v>
       </c>
-      <c r="M87" t="s" s="2">
+      <c r="N87" t="s" s="2">
         <v>592</v>
       </c>
-      <c r="N87" t="s" s="2">
+      <c r="O87" t="s" s="2">
         <v>593</v>
-      </c>
-      <c r="O87" t="s" s="2">
-        <v>594</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>36</v>
@@ -12763,7 +12761,7 @@
         <v>36</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>46</v>
@@ -12781,7 +12779,7 @@
         <v>36</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="AM87" t="s" s="2">
         <v>305</v>
@@ -12798,10 +12796,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12824,16 +12822,16 @@
         <v>47</v>
       </c>
       <c r="K88" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="L88" t="s" s="2">
         <v>597</v>
       </c>
-      <c r="L88" t="s" s="2">
+      <c r="M88" t="s" s="2">
         <v>598</v>
       </c>
-      <c r="M88" t="s" s="2">
+      <c r="N88" t="s" s="2">
         <v>599</v>
-      </c>
-      <c r="N88" t="s" s="2">
-        <v>600</v>
       </c>
       <c r="O88" t="s" s="2">
         <v>391</v>
@@ -12864,11 +12862,11 @@
         <v>200</v>
       </c>
       <c r="Y88" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="Z88" t="s" s="2">
         <v>601</v>
       </c>
-      <c r="Z88" t="s" s="2">
-        <v>602</v>
-      </c>
       <c r="AA88" t="s" s="2">
         <v>36</v>
       </c>
@@ -12885,7 +12883,7 @@
         <v>36</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>34</v>
@@ -12894,7 +12892,7 @@
         <v>46</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="AJ88" t="s" s="2">
         <v>59</v>
@@ -12903,27 +12901,27 @@
         <v>36</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="AM88" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="AN88" t="s" s="2">
         <v>395</v>
       </c>
-      <c r="AN88" t="s" s="2">
+      <c r="AO88" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AP88" t="s" s="2">
         <v>396</v>
-      </c>
-      <c r="AO88" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AP88" t="s" s="2">
-        <v>397</v>
       </c>
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12949,16 +12947,16 @@
         <v>209</v>
       </c>
       <c r="L89" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="M89" t="s" s="2">
         <v>606</v>
       </c>
-      <c r="M89" t="s" s="2">
+      <c r="N89" t="s" s="2">
         <v>607</v>
       </c>
-      <c r="N89" t="s" s="2">
-        <v>608</v>
-      </c>
       <c r="O89" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>36</v>
@@ -12986,11 +12984,11 @@
         <v>106</v>
       </c>
       <c r="Y89" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="Z89" t="s" s="2">
         <v>448</v>
       </c>
-      <c r="Z89" t="s" s="2">
-        <v>449</v>
-      </c>
       <c r="AA89" t="s" s="2">
         <v>36</v>
       </c>
@@ -13007,7 +13005,7 @@
         <v>36</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>34</v>
@@ -13016,7 +13014,7 @@
         <v>46</v>
       </c>
       <c r="AI89" t="s" s="2">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="AJ89" t="s" s="2">
         <v>59</v>
@@ -13031,7 +13029,7 @@
         <v>60</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>36</v>
@@ -13042,14 +13040,14 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
@@ -13071,16 +13069,16 @@
         <v>209</v>
       </c>
       <c r="L90" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="M90" t="s" s="2">
         <v>454</v>
       </c>
-      <c r="M90" t="s" s="2">
+      <c r="N90" t="s" s="2">
         <v>455</v>
       </c>
-      <c r="N90" t="s" s="2">
+      <c r="O90" t="s" s="2">
         <v>456</v>
-      </c>
-      <c r="O90" t="s" s="2">
-        <v>457</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>36</v>
@@ -13108,11 +13106,11 @@
         <v>106</v>
       </c>
       <c r="Y90" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="Z90" t="s" s="2">
         <v>458</v>
       </c>
-      <c r="Z90" t="s" s="2">
-        <v>459</v>
-      </c>
       <c r="AA90" t="s" s="2">
         <v>36</v>
       </c>
@@ -13129,7 +13127,7 @@
         <v>36</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>34</v>
@@ -13147,27 +13145,27 @@
         <v>36</v>
       </c>
       <c r="AL90" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="AM90" t="s" s="2">
         <v>460</v>
       </c>
-      <c r="AM90" t="s" s="2">
+      <c r="AN90" t="s" s="2">
         <v>461</v>
       </c>
-      <c r="AN90" t="s" s="2">
+      <c r="AO90" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AP90" t="s" s="2">
         <v>462</v>
-      </c>
-      <c r="AO90" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AP90" t="s" s="2">
-        <v>463</v>
       </c>
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13193,16 +13191,16 @@
         <v>37</v>
       </c>
       <c r="L91" t="s" s="2">
+        <v>611</v>
+      </c>
+      <c r="M91" t="s" s="2">
         <v>612</v>
       </c>
-      <c r="M91" t="s" s="2">
-        <v>613</v>
-      </c>
       <c r="N91" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="O91" t="s" s="2">
         <v>513</v>
-      </c>
-      <c r="O91" t="s" s="2">
-        <v>514</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>36</v>
@@ -13251,7 +13249,7 @@
         <v>36</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>34</v>
@@ -13272,10 +13270,10 @@
         <v>36</v>
       </c>
       <c r="AM91" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="AN91" t="s" s="2">
         <v>516</v>
-      </c>
-      <c r="AN91" t="s" s="2">
-        <v>517</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>36</v>
